--- a/backend/database/golive_20260501/golive_filled_20260501.xlsx
+++ b/backend/database/golive_20260501/golive_filled_20260501.xlsx
@@ -17,7 +17,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="2/reCKtNL/uHHGFhqI2TVTkICKVkz33vcfrz73yEUYk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="A2fLzSBY4+ZefTU9O0yqaVoQGctD0XyRnrIbiQUXRSI="/>
     </ext>
   </extLst>
 </workbook>
@@ -526,7 +526,7 @@
       <name val="&quot;JetBrains Mono&quot;"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -571,8 +571,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD0E0E3"/>
-        <bgColor rgb="FFD0E0E3"/>
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -591,6 +591,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1A2F52"/>
         <bgColor rgb="FF1A2F52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E0E3"/>
+        <bgColor rgb="FFD0E0E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -635,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -660,14 +666,14 @@
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
@@ -687,6 +693,9 @@
     <xf borderId="4" fillId="7" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -731,12 +740,17 @@
     <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="12" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="4" fillId="12" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="9" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2180,24 +2194,24 @@
       <c r="B4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="7">
-        <v>12.0</v>
+      <c r="C4" s="8">
+        <v>24.0</v>
       </c>
       <c r="D4" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="8">
-        <v>4.0</v>
-      </c>
-      <c r="G4" s="9">
-        <f t="shared" ref="G4:G24" si="1">E4*D4+F4*C4</f>
-        <v>48</v>
-      </c>
-      <c r="H4" s="10">
-        <v>0.0</v>
+        <f t="shared" ref="D4:D22" si="1">C4*12</f>
+        <v>288</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="9">
+        <v>3.0</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>326.04</v>
       </c>
       <c r="I4" s="11"/>
     </row>
@@ -2208,24 +2222,24 @@
       <c r="B5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="7">
-        <v>12.0</v>
+      <c r="C5" s="8">
+        <v>24.0</v>
       </c>
       <c r="D5" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="8">
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="9">
         <v>1.0</v>
       </c>
-      <c r="G5" s="9">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="H5" s="10">
-        <v>0.0</v>
+      <c r="G5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>208.33</v>
       </c>
       <c r="I5" s="11"/>
     </row>
@@ -2236,24 +2250,24 @@
       <c r="B6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="7">
-        <v>12.0</v>
+      <c r="C6" s="8">
+        <v>24.0</v>
       </c>
       <c r="D6" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="8">
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="9">
         <v>5.0</v>
       </c>
-      <c r="G6" s="9">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0.0</v>
+      <c r="G6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>207.62</v>
       </c>
       <c r="I6" s="11"/>
     </row>
@@ -2264,24 +2278,24 @@
       <c r="B7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="7">
-        <v>12.0</v>
+      <c r="C7" s="8">
+        <v>24.0</v>
       </c>
       <c r="D7" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="8">
-        <v>11.0</v>
-      </c>
-      <c r="G7" s="9">
-        <f t="shared" si="1"/>
-        <v>132</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>190.97</v>
       </c>
       <c r="I7" s="11"/>
     </row>
@@ -2292,24 +2306,24 @@
       <c r="B8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="7">
-        <v>12.0</v>
+      <c r="C8" s="8">
+        <v>24.0</v>
       </c>
       <c r="D8" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>188.0</v>
       </c>
       <c r="I8" s="11"/>
     </row>
@@ -2320,24 +2334,24 @@
       <c r="B9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="7">
-        <v>12.0</v>
+      <c r="C9" s="8">
+        <v>24.0</v>
       </c>
       <c r="D9" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>187.75</v>
       </c>
       <c r="I9" s="11"/>
     </row>
@@ -2348,24 +2362,24 @@
       <c r="B10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="7">
-        <v>12.0</v>
+      <c r="C10" s="8">
+        <v>24.0</v>
       </c>
       <c r="D10" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E10" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F10" s="8">
-        <v>8.0</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="H10" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>104.16</v>
       </c>
       <c r="I10" s="11"/>
     </row>
@@ -2376,24 +2390,24 @@
       <c r="B11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="7">
-        <v>12.0</v>
+      <c r="C11" s="8">
+        <v>24.0</v>
       </c>
       <c r="D11" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F11" s="8">
-        <v>15.0</v>
-      </c>
-      <c r="G11" s="9">
-        <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="H11" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>79.86</v>
       </c>
       <c r="I11" s="11"/>
     </row>
@@ -2404,24 +2418,24 @@
       <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="7">
-        <v>12.0</v>
+      <c r="C12" s="8">
+        <v>24.0</v>
       </c>
       <c r="D12" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E12" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>184.02</v>
       </c>
       <c r="I12" s="11"/>
     </row>
@@ -2432,24 +2446,24 @@
       <c r="B13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="7">
-        <v>12.0</v>
+      <c r="C13" s="8">
+        <v>24.0</v>
       </c>
       <c r="D13" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E13" s="9">
         <v>1.0</v>
       </c>
-      <c r="F13" s="8">
-        <v>10.0</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="1"/>
-        <v>264</v>
-      </c>
-      <c r="H13" s="10">
-        <v>0.0</v>
+      <c r="F13" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>83.33</v>
       </c>
       <c r="I13" s="11"/>
     </row>
@@ -2460,24 +2474,24 @@
       <c r="B14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="7">
-        <v>12.0</v>
+      <c r="C14" s="8">
+        <v>24.0</v>
       </c>
       <c r="D14" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E14" s="9">
         <v>1.0</v>
       </c>
-      <c r="F14" s="8">
-        <v>7.0</v>
-      </c>
-      <c r="G14" s="9">
-        <f t="shared" si="1"/>
-        <v>228</v>
-      </c>
-      <c r="H14" s="10">
-        <v>0.0</v>
+      <c r="F14" s="9">
+        <v>5.0</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>246.52</v>
       </c>
       <c r="I14" s="11"/>
     </row>
@@ -2488,24 +2502,24 @@
       <c r="B15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="7">
-        <v>12.0</v>
+      <c r="C15" s="8">
+        <v>24.0</v>
       </c>
       <c r="D15" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="8">
-        <v>8.0</v>
-      </c>
-      <c r="G15" s="9">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="H15" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>121.52</v>
       </c>
       <c r="I15" s="11"/>
     </row>
@@ -2516,24 +2530,24 @@
       <c r="B16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="7">
-        <v>12.0</v>
+      <c r="C16" s="8">
+        <v>24.0</v>
       </c>
       <c r="D16" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E16" s="8">
-        <v>6.0</v>
-      </c>
-      <c r="F16" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="1"/>
-        <v>888</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E16" s="9">
+        <v>5.0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>232.63</v>
       </c>
       <c r="I16" s="11"/>
     </row>
@@ -2544,24 +2558,24 @@
       <c r="B17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="7">
-        <v>12.0</v>
+      <c r="C17" s="8">
+        <v>24.0</v>
       </c>
       <c r="D17" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="9">
-        <f t="shared" si="1"/>
-        <v>144</v>
-      </c>
-      <c r="H17" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>118.05</v>
       </c>
       <c r="I17" s="11"/>
     </row>
@@ -2572,24 +2586,24 @@
       <c r="B18" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="7">
-        <v>12.0</v>
+      <c r="C18" s="8">
+        <v>24.0</v>
       </c>
       <c r="D18" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="9">
         <f t="shared" si="1"/>
         <v>288</v>
       </c>
-      <c r="H18" s="10">
-        <v>0.0</v>
+      <c r="E18" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>118.05</v>
       </c>
       <c r="I18" s="11"/>
     </row>
@@ -2600,24 +2614,24 @@
       <c r="B19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="7">
-        <v>12.0</v>
+      <c r="C19" s="8">
+        <v>24.0</v>
       </c>
       <c r="D19" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E19" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F19" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>175.0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
@@ -2628,24 +2642,24 @@
       <c r="B20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="7">
-        <v>12.0</v>
+      <c r="C20" s="8">
+        <v>24.0</v>
       </c>
       <c r="D20" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F20" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>166.66</v>
       </c>
       <c r="I20" s="11"/>
     </row>
@@ -2656,24 +2670,24 @@
       <c r="B21" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="7">
-        <v>12.0</v>
+      <c r="C21" s="8">
+        <v>24.0</v>
       </c>
       <c r="D21" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F21" s="8">
-        <v>10.0</v>
-      </c>
-      <c r="G21" s="9">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="H21" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>111.11</v>
       </c>
       <c r="I21" s="11"/>
     </row>
@@ -2684,24 +2698,24 @@
       <c r="B22" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="7">
-        <v>12.0</v>
+      <c r="C22" s="8">
+        <v>24.0</v>
       </c>
       <c r="D22" s="7">
-        <v>144.0</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="F22" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="G22" s="9">
-        <f t="shared" si="1"/>
-        <v>204</v>
-      </c>
-      <c r="H22" s="10">
-        <v>0.0</v>
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>118.05</v>
       </c>
       <c r="I22" s="11"/>
     </row>
@@ -2716,20 +2730,20 @@
         <v>10.0</v>
       </c>
       <c r="D23" s="7">
-        <v>120.0</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F23" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="10">
-        <v>0.0</v>
+        <f>C23*10</f>
+        <v>100</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>350.0</v>
       </c>
       <c r="I23" s="11"/>
     </row>
@@ -2744,20 +2758,20 @@
         <v>10.0</v>
       </c>
       <c r="D24" s="7">
-        <v>120.0</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="F24" s="8">
-        <v>4.0</v>
-      </c>
-      <c r="G24" s="9">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="H24" s="10">
-        <v>0.0</v>
+        <f>C24*20</f>
+        <v>200</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>170.0</v>
       </c>
       <c r="I24" s="11"/>
     </row>
@@ -3820,11 +3834,11 @@
         <v>0.0</v>
       </c>
       <c r="E5" s="17">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="F5" s="18">
         <f t="shared" ref="F5:F88" si="1">IF(B5="","",C5*IFERROR(VLOOKUP(B5,$J$6:$K$26,2,FALSE),0)*12+D5*IFERROR(VLOOKUP(B5,$J$6:$K$26,2,FALSE),0)+E5)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G5" s="19"/>
       <c r="J5" s="20"/>
@@ -3869,14 +3883,14 @@
         <v>0.0</v>
       </c>
       <c r="D7" s="17">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="E7" s="17">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="F7" s="18">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G7" s="19"/>
       <c r="J7" s="20" t="s">
@@ -4068,11 +4082,11 @@
         <v>0.0</v>
       </c>
       <c r="E14" s="17">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="F14" s="18">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G14" s="19"/>
       <c r="J14" s="20" t="s">
@@ -4096,11 +4110,11 @@
         <v>0.0</v>
       </c>
       <c r="E15" s="17">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="F15" s="18">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15" s="19"/>
       <c r="J15" s="20" t="s">
@@ -4121,14 +4135,14 @@
         <v>0.0</v>
       </c>
       <c r="D16" s="17">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E16" s="17">
         <v>0.0</v>
       </c>
       <c r="F16" s="18">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G16" s="19"/>
       <c r="J16" s="20" t="s">
@@ -4149,14 +4163,14 @@
         <v>0.0</v>
       </c>
       <c r="D17" s="17">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E17" s="17">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="F17" s="18">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G17" s="19"/>
       <c r="J17" s="20" t="s">
@@ -4208,11 +4222,11 @@
         <v>0.0</v>
       </c>
       <c r="E19" s="17">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="F19" s="18">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G19" s="19"/>
       <c r="J19" s="20" t="s">
@@ -4236,11 +4250,11 @@
         <v>0.0</v>
       </c>
       <c r="E20" s="17">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="F20" s="18">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G20" s="19"/>
       <c r="J20" s="20" t="s">
@@ -4261,14 +4275,14 @@
         <v>0.0</v>
       </c>
       <c r="D21" s="17">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="E21" s="17">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="F21" s="18">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G21" s="19"/>
       <c r="J21" s="20" t="s">
@@ -4373,14 +4387,14 @@
         <v>0.0</v>
       </c>
       <c r="D25" s="17">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="E25" s="17">
         <v>0.0</v>
       </c>
       <c r="F25" s="18">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G25" s="19"/>
       <c r="J25" s="20" t="s">
@@ -4400,17 +4414,17 @@
       <c r="C26" s="24">
         <v>0.0</v>
       </c>
-      <c r="D26" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="E26" s="24">
-        <v>12.0</v>
-      </c>
-      <c r="F26" s="25">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="G26" s="26"/>
+      <c r="D26" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="E26" s="25">
+        <v>11.0</v>
+      </c>
+      <c r="F26" s="26">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="G26" s="27"/>
       <c r="J26" s="20" t="s">
         <v>63</v>
       </c>
@@ -4428,17 +4442,17 @@
       <c r="C27" s="24">
         <v>0.0</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="25">
         <v>1.0</v>
       </c>
-      <c r="E27" s="24">
-        <v>4.0</v>
-      </c>
-      <c r="F27" s="25">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="G27" s="26"/>
+      <c r="E27" s="25">
+        <v>13.0</v>
+      </c>
+      <c r="F27" s="26">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="G27" s="27"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="23" t="s">
@@ -4450,17 +4464,17 @@
       <c r="C28" s="24">
         <v>0.0</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="25">
         <v>1.0</v>
       </c>
-      <c r="E28" s="24">
-        <v>6.0</v>
-      </c>
-      <c r="F28" s="25">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="G28" s="26"/>
+      <c r="E28" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="F28" s="26">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G28" s="27"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="23" t="s">
@@ -4472,15 +4486,15 @@
       <c r="C29" s="24">
         <v>0.0</v>
       </c>
-      <c r="D29" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="E29" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="F29" s="25">
-        <f t="shared" si="1"/>
-        <v>12</v>
+      <c r="D29" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="E29" s="25">
+        <v>8.0</v>
+      </c>
+      <c r="F29" s="26">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="G29" s="19"/>
     </row>
@@ -4494,17 +4508,17 @@
       <c r="C30" s="24">
         <v>0.0</v>
       </c>
-      <c r="D30" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="E30" s="24">
-        <v>6.0</v>
-      </c>
-      <c r="F30" s="25">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="G30" s="26"/>
+      <c r="D30" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="E30" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="F30" s="26">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="G30" s="27"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="23" t="s">
@@ -4516,17 +4530,17 @@
       <c r="C31" s="24">
         <v>0.0</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <v>1.0</v>
       </c>
-      <c r="E31" s="24">
-        <v>8.0</v>
-      </c>
-      <c r="F31" s="25">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="G31" s="26"/>
+      <c r="E31" s="25">
+        <v>5.0</v>
+      </c>
+      <c r="F31" s="26">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="23" t="s">
@@ -4538,17 +4552,17 @@
       <c r="C32" s="24">
         <v>0.0</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="25">
         <v>1.0</v>
       </c>
-      <c r="E32" s="24">
-        <v>9.0</v>
-      </c>
-      <c r="F32" s="25">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="G32" s="26"/>
+      <c r="E32" s="25">
+        <v>7.0</v>
+      </c>
+      <c r="F32" s="26">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="23" t="s">
@@ -4560,17 +4574,17 @@
       <c r="C33" s="24">
         <v>0.0</v>
       </c>
-      <c r="D33" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="24">
-        <v>12.0</v>
-      </c>
-      <c r="F33" s="25">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="G33" s="26"/>
+      <c r="D33" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="E33" s="25">
+        <v>7.0</v>
+      </c>
+      <c r="F33" s="26">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="23" t="s">
@@ -4582,17 +4596,17 @@
       <c r="C34" s="24">
         <v>0.0</v>
       </c>
-      <c r="D34" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="E34" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="25">
+      <c r="D34" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="23" t="s">
@@ -4604,17 +4618,17 @@
       <c r="C35" s="24">
         <v>0.0</v>
       </c>
-      <c r="D35" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="E35" s="24">
-        <v>18.0</v>
-      </c>
-      <c r="F35" s="25">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G35" s="26"/>
+      <c r="D35" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="25">
+        <v>12.0</v>
+      </c>
+      <c r="F35" s="26">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G35" s="27"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="23" t="s">
@@ -4626,17 +4640,17 @@
       <c r="C36" s="24">
         <v>0.0</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="E36" s="25">
         <v>2.0</v>
       </c>
-      <c r="E36" s="24">
-        <v>17.0</v>
-      </c>
-      <c r="F36" s="25">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="G36" s="26"/>
+      <c r="F36" s="26">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="G36" s="27"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="23" t="s">
@@ -4648,17 +4662,17 @@
       <c r="C37" s="24">
         <v>0.0</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="25">
         <v>3.0</v>
       </c>
-      <c r="E37" s="24">
-        <v>5.0</v>
-      </c>
-      <c r="F37" s="25">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="G37" s="26"/>
+      <c r="E37" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="F37" s="26">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="G37" s="27"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="23" t="s">
@@ -4670,17 +4684,17 @@
       <c r="C38" s="24">
         <v>0.0</v>
       </c>
-      <c r="D38" s="24">
-        <v>3.0</v>
-      </c>
-      <c r="E38" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="F38" s="25">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="G38" s="26"/>
+      <c r="D38" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="E38" s="25">
+        <v>17.0</v>
+      </c>
+      <c r="F38" s="26">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="23" t="s">
@@ -4692,17 +4706,17 @@
       <c r="C39" s="24">
         <v>0.0</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="25">
         <v>1.0</v>
       </c>
-      <c r="E39" s="24">
-        <v>14.0</v>
-      </c>
-      <c r="F39" s="25">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="G39" s="26"/>
+      <c r="E39" s="25">
+        <v>8.0</v>
+      </c>
+      <c r="F39" s="26">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="G39" s="27"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="23" t="s">
@@ -4714,17 +4728,17 @@
       <c r="C40" s="24">
         <v>0.0</v>
       </c>
-      <c r="D40" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="E40" s="24">
-        <v>22.0</v>
-      </c>
-      <c r="F40" s="25">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="G40" s="26"/>
+      <c r="D40" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="E40" s="25">
+        <v>12.0</v>
+      </c>
+      <c r="F40" s="26">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="G40" s="27"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="23" t="s">
@@ -4736,17 +4750,17 @@
       <c r="C41" s="24">
         <v>0.0</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="25">
         <v>2.0</v>
       </c>
-      <c r="E41" s="24">
-        <v>9.0</v>
-      </c>
-      <c r="F41" s="25">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="G41" s="26"/>
+      <c r="E41" s="25">
+        <v>23.0</v>
+      </c>
+      <c r="F41" s="26">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="G41" s="27"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="23" t="s">
@@ -4758,17 +4772,17 @@
       <c r="C42" s="24">
         <v>0.0</v>
       </c>
-      <c r="D42" s="24">
-        <v>7.0</v>
-      </c>
-      <c r="E42" s="24">
-        <v>13.0</v>
-      </c>
-      <c r="F42" s="25">
-        <f t="shared" si="1"/>
-        <v>97</v>
-      </c>
-      <c r="G42" s="26"/>
+      <c r="D42" s="25">
+        <v>4.0</v>
+      </c>
+      <c r="E42" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="F42" s="26">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="G42" s="27"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="23" t="s">
@@ -4780,17 +4794,17 @@
       <c r="C43" s="24">
         <v>0.0</v>
       </c>
-      <c r="D43" s="24">
-        <v>2.0</v>
-      </c>
-      <c r="E43" s="24">
-        <v>18.0</v>
-      </c>
-      <c r="F43" s="25">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-      <c r="G43" s="26"/>
+      <c r="D43" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="E43" s="25">
+        <v>10.0</v>
+      </c>
+      <c r="F43" s="26">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="G43" s="27"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="23" t="s">
@@ -4802,17 +4816,17 @@
       <c r="C44" s="24">
         <v>0.0</v>
       </c>
-      <c r="D44" s="24">
-        <v>3.0</v>
-      </c>
-      <c r="E44" s="24">
-        <v>9.0</v>
-      </c>
-      <c r="F44" s="25">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="G44" s="26"/>
+      <c r="D44" s="25">
+        <v>7.0</v>
+      </c>
+      <c r="E44" s="25">
+        <v>5.0</v>
+      </c>
+      <c r="F44" s="26">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="G44" s="27"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="23" t="s">
@@ -4824,15 +4838,15 @@
       <c r="C45" s="24">
         <v>0.0</v>
       </c>
-      <c r="D45" s="24">
-        <v>16.0</v>
-      </c>
-      <c r="E45" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="F45" s="25">
-        <f t="shared" si="1"/>
-        <v>160</v>
+      <c r="D45" s="25">
+        <v>4.0</v>
+      </c>
+      <c r="E45" s="25">
+        <v>9.0</v>
+      </c>
+      <c r="F45" s="26">
+        <f t="shared" si="1"/>
+        <v>49</v>
       </c>
       <c r="G45" s="19"/>
     </row>
@@ -4846,932 +4860,950 @@
       <c r="C46" s="24">
         <v>0.0</v>
       </c>
-      <c r="D46" s="24">
-        <v>10.0</v>
-      </c>
-      <c r="E46" s="24">
-        <v>9.0</v>
-      </c>
-      <c r="F46" s="25">
-        <f t="shared" si="1"/>
-        <v>109</v>
+      <c r="D46" s="25">
+        <v>4.0</v>
+      </c>
+      <c r="E46" s="25">
+        <v>6.0</v>
+      </c>
+      <c r="F46" s="26">
+        <f t="shared" si="1"/>
+        <v>46</v>
       </c>
       <c r="G46" s="19"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D47" s="29"/>
-      <c r="E47" s="28">
+      <c r="C47" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D47" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E47" s="29">
         <v>20.0</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F47" s="30">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="G47" s="26"/>
+      <c r="G47" s="27"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D48" s="29"/>
-      <c r="E48" s="28">
+      <c r="C48" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D48" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E48" s="29">
         <v>19.0</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="30">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="G48" s="26"/>
+      <c r="G48" s="27"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D49" s="29"/>
-      <c r="E49" s="28">
+      <c r="C49" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D49" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E49" s="29">
         <v>22.0</v>
       </c>
-      <c r="F49" s="29">
+      <c r="F49" s="30">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="G49" s="26"/>
+      <c r="G49" s="27"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D50" s="28">
+      <c r="C50" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D50" s="29">
         <v>1.0</v>
       </c>
-      <c r="E50" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="F50" s="29">
+      <c r="E50" s="29">
+        <v>2.0</v>
+      </c>
+      <c r="F50" s="30">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="G50" s="27"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D51" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="E51" s="29">
+        <v>2.0</v>
+      </c>
+      <c r="F51" s="30">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="G51" s="27"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D52" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E52" s="29">
+        <v>20.0</v>
+      </c>
+      <c r="F52" s="30">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="G52" s="27"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D53" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E53" s="29">
+        <v>21.0</v>
+      </c>
+      <c r="F53" s="30">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="G53" s="27"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D54" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E54" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="F54" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="27"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C55" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D55" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E55" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="F55" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G55" s="27"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D56" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E56" s="29">
+        <v>19.0</v>
+      </c>
+      <c r="F56" s="30">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G56" s="27"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D57" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="E57" s="29">
+        <v>31.0</v>
+      </c>
+      <c r="F57" s="30">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="G57" s="27"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D58" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="E58" s="29">
+        <v>22.0</v>
+      </c>
+      <c r="F58" s="30">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="G58" s="27"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D59" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="E59" s="29">
+        <v>29.0</v>
+      </c>
+      <c r="F59" s="30">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="G59" s="27"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D60" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E60" s="29">
+        <v>17.0</v>
+      </c>
+      <c r="F60" s="30">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="G60" s="27"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C61" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D61" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="E61" s="29">
+        <v>57.0</v>
+      </c>
+      <c r="F61" s="30">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="G61" s="27"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C62" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D62" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="E62" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="F62" s="30">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="G62" s="27"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D63" s="29">
+        <v>3.0</v>
+      </c>
+      <c r="E63" s="29">
+        <v>7.0</v>
+      </c>
+      <c r="F63" s="30">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="G63" s="27"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C64" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D64" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="E64" s="29">
+        <v>15.0</v>
+      </c>
+      <c r="F64" s="30">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="G64" s="27"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C65" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D65" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E65" s="29">
+        <v>8.0</v>
+      </c>
+      <c r="F65" s="30">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G65" s="27"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D66" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="E66" s="29">
+        <v>5.0</v>
+      </c>
+      <c r="F66" s="30">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="G66" s="31"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D67" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="E67" s="29">
+        <v>4.0</v>
+      </c>
+      <c r="F67" s="30">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G67" s="31"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C68" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D68" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E68" s="34">
+        <v>22.0</v>
+      </c>
+      <c r="F68" s="35">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="G68" s="31"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D69" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="E69" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="F69" s="35">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G50" s="26"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="27" t="s">
+      <c r="G69" s="31"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C70" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D70" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E70" s="36">
+        <v>12.0</v>
+      </c>
+      <c r="F70" s="35">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G70" s="31"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C71" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D71" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E71" s="36">
+        <v>12.0</v>
+      </c>
+      <c r="F71" s="35">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G71" s="31"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D51" s="28">
+      <c r="C72" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D72" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E72" s="36">
+        <v>23.0</v>
+      </c>
+      <c r="F72" s="35">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="G72" s="31"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D73" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E73" s="36">
+        <v>21.0</v>
+      </c>
+      <c r="F73" s="35">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="G73" s="31"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D74" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E74" s="36">
+        <v>23.0</v>
+      </c>
+      <c r="F74" s="35">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="G74" s="31"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D75" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E75" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="F75" s="35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="31"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B76" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D76" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E76" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="F76" s="35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G76" s="31"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B77" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D77" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E77" s="36">
+        <v>19.0</v>
+      </c>
+      <c r="F77" s="35">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G77" s="31"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B78" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D78" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E78" s="36">
+        <v>16.0</v>
+      </c>
+      <c r="F78" s="35">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="G78" s="31"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B79" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D79" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E79" s="36">
+        <v>19.0</v>
+      </c>
+      <c r="F79" s="35">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G79" s="31"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C80" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D80" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E80" s="36">
+        <v>21.0</v>
+      </c>
+      <c r="F80" s="35">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="G80" s="31"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C81" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D81" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E81" s="36">
+        <v>16.0</v>
+      </c>
+      <c r="F81" s="35">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="G81" s="31"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B82" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C82" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D82" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E82" s="36">
+        <v>14.0</v>
+      </c>
+      <c r="F82" s="35">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="G82" s="31"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C83" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D83" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E83" s="36">
+        <v>19.0</v>
+      </c>
+      <c r="F83" s="35">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G83" s="31"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C84" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D84" s="36">
         <v>1.0</v>
       </c>
-      <c r="E51" s="28">
-        <v>2.0</v>
-      </c>
-      <c r="F51" s="29">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="G51" s="26"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B52" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D52" s="29"/>
-      <c r="E52" s="28">
-        <v>20.0</v>
-      </c>
-      <c r="F52" s="29">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="G52" s="26"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D53" s="29"/>
-      <c r="E53" s="28">
-        <v>21.0</v>
-      </c>
-      <c r="F53" s="29">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="G53" s="26"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D54" s="29"/>
-      <c r="E54" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="F54" s="29">
+      <c r="E84" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="F84" s="35">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="G84" s="31"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C85" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D85" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E85" s="36">
+        <v>23.0</v>
+      </c>
+      <c r="F85" s="35">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="G85" s="31"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C86" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D86" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="E86" s="36">
+        <v>12.0</v>
+      </c>
+      <c r="F86" s="35">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="G86" s="31"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B87" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C87" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D87" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E87" s="36">
+        <v>4.0</v>
+      </c>
+      <c r="F87" s="35">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G87" s="31"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B88" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C88" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D88" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E88" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="F88" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G54" s="26"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C55" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D55" s="29"/>
-      <c r="E55" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="F55" s="29">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="26"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B56" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D56" s="29"/>
-      <c r="E56" s="28">
-        <v>19.0</v>
-      </c>
-      <c r="F56" s="29">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="G56" s="26"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C57" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D57" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E57" s="28">
-        <v>15.0</v>
-      </c>
-      <c r="F57" s="29">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="G57" s="26"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C58" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D58" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E58" s="28">
-        <v>3.0</v>
-      </c>
-      <c r="F58" s="29">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="G58" s="26"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C59" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D59" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E59" s="28">
-        <v>14.0</v>
-      </c>
-      <c r="F59" s="29">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="G59" s="26"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B60" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C60" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D60" s="29"/>
-      <c r="E60" s="28">
-        <v>17.0</v>
-      </c>
-      <c r="F60" s="29">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="G60" s="26"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B61" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C61" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D61" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E61" s="28">
-        <v>12.0</v>
-      </c>
-      <c r="F61" s="29">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="G61" s="26"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C62" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D62" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E62" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F62" s="29">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="G62" s="26"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C63" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D63" s="28">
-        <v>3.0</v>
-      </c>
-      <c r="E63" s="28">
-        <v>7.0</v>
-      </c>
-      <c r="F63" s="29">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-      <c r="G63" s="26"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C64" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D64" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E64" s="28">
-        <v>15.0</v>
-      </c>
-      <c r="F64" s="29">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="G64" s="26"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C65" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D65" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E65" s="28">
-        <v>8.0</v>
-      </c>
-      <c r="F65" s="29">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="G65" s="26"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B66" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D66" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E66" s="28">
-        <v>5.0</v>
-      </c>
-      <c r="F66" s="29">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="G66" s="30"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B67" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C67" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D67" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="E67" s="28">
-        <v>3.0</v>
-      </c>
-      <c r="F67" s="29">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="G67" s="30"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C68" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D68" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E68" s="33">
-        <v>23.0</v>
-      </c>
-      <c r="F68" s="34">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="G68" s="30"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B69" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="C69" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D69" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E69" s="35">
-        <v>21.0</v>
-      </c>
-      <c r="F69" s="34">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="G69" s="30"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B70" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C70" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D70" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E70" s="35">
-        <v>23.0</v>
-      </c>
-      <c r="F70" s="34">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="G70" s="30"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B71" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="C71" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D71" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E71" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="F71" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G71" s="30"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B72" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C72" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D72" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E72" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="F72" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G72" s="30"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C73" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D73" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E73" s="35">
-        <v>19.0</v>
-      </c>
-      <c r="F73" s="34">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="G73" s="30"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B74" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C74" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D74" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E74" s="35">
-        <v>16.0</v>
-      </c>
-      <c r="F74" s="34">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="G74" s="30"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B75" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C75" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D75" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E75" s="35">
-        <v>19.0</v>
-      </c>
-      <c r="F75" s="34">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="G75" s="30"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B76" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C76" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D76" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E76" s="35">
-        <v>21.0</v>
-      </c>
-      <c r="F76" s="34">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="G76" s="30"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B77" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C77" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D77" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E77" s="35">
-        <v>16.0</v>
-      </c>
-      <c r="F77" s="34">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="G77" s="30"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B78" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C78" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D78" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E78" s="35">
-        <v>14.0</v>
-      </c>
-      <c r="F78" s="34">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="G78" s="30"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B79" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C79" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D79" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E79" s="35">
-        <v>19.0</v>
-      </c>
-      <c r="F79" s="34">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="G79" s="30"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B80" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="C80" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D80" s="35">
-        <v>1.0</v>
-      </c>
-      <c r="E80" s="35">
-        <v>1.0</v>
-      </c>
-      <c r="F80" s="34">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="G80" s="30"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B81" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C81" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D81" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E81" s="35">
-        <v>23.0</v>
-      </c>
-      <c r="F81" s="34">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="G81" s="30"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B82" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C82" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D82" s="35">
-        <v>1.0</v>
-      </c>
-      <c r="E82" s="35">
-        <v>12.0</v>
-      </c>
-      <c r="F82" s="34">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="G82" s="30"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B83" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C83" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D83" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E83" s="35">
-        <v>22.0</v>
-      </c>
-      <c r="F83" s="34">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="G83" s="30"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B84" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C84" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D84" s="35">
-        <v>1.0</v>
-      </c>
-      <c r="E84" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="F84" s="34">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="G84" s="30"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B85" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C85" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D85" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E85" s="35">
-        <v>12.0</v>
-      </c>
-      <c r="F85" s="34">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="G85" s="30"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B86" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C86" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D86" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E86" s="35">
-        <v>12.0</v>
-      </c>
-      <c r="F86" s="34">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="G86" s="30"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B87" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C87" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D87" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E87" s="35">
-        <v>4.0</v>
-      </c>
-      <c r="F87" s="34">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G87" s="30"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B88" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C88" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D88" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E88" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="F88" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G88" s="30"/>
+      <c r="G88" s="31"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="31"/>
-      <c r="B89" s="32"/>
-      <c r="C89" s="35"/>
-      <c r="D89" s="35"/>
-      <c r="E89" s="35"/>
-      <c r="F89" s="34"/>
-      <c r="G89" s="30"/>
+      <c r="A89" s="32"/>
+      <c r="B89" s="33"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="35"/>
+      <c r="G89" s="31"/>
     </row>
     <row r="90" ht="15.75" customHeight="1"/>
     <row r="91" ht="15.75" customHeight="1"/>
@@ -5782,18 +5814,18 @@
     <row r="96" ht="15.75" customHeight="1"/>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="36" t="s">
+      <c r="A98" s="37" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="37" t="s">
+      <c r="A99" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="B99" s="37" t="s">
+      <c r="B99" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C99" s="38" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5809,7 +5841,7 @@
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="38" t="s">
+      <c r="A101" s="39" t="s">
         <v>72</v>
       </c>
       <c r="B101" s="21" t="s">
@@ -6809,628 +6841,628 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="40" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C3" s="43">
         <v>9.0</v>
       </c>
-      <c r="D3" s="42">
+      <c r="D3" s="43">
         <v>11.0</v>
       </c>
-      <c r="E3" s="42">
+      <c r="E3" s="43">
         <v>12.0</v>
       </c>
-      <c r="F3" s="42">
+      <c r="F3" s="43">
         <v>12.0</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="44" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="42">
+      <c r="C4" s="43">
         <v>8.0</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="43">
         <v>12.0</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="43">
         <v>12.0</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="43">
         <v>10.0</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="44" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="43">
         <v>22.0</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="43">
         <v>16.0</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="43">
         <v>24.0</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="43">
         <v>22.0</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="44" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="43">
         <v>20.0</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="43">
         <v>17.0</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="43">
         <v>24.0</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="43">
         <v>5.0</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="44" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="43">
         <v>12.0</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="43">
         <v>12.0</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="43">
         <v>12.0</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="43">
         <v>7.0</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="43">
         <v>12.0</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="43">
         <v>12.0</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="43">
         <v>12.0</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="43">
         <v>9.0</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="44" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="43">
         <v>12.0</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="43">
         <v>11.0</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="43">
         <v>12.0</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="43">
         <v>10.0</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="44" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="43">
         <v>12.0</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="43">
         <v>8.0</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="44" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="44" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="43">
         <v>11.0</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="43">
         <v>9.0</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="43">
         <v>12.0</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="43">
         <v>8.0</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="44" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="43">
         <v>9.0</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="43">
         <v>11.0</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="43">
         <v>12.0</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="43">
         <v>12.0</v>
       </c>
-      <c r="G13" s="43" t="s">
+      <c r="G13" s="44" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="43">
         <v>8.0</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="43">
         <v>8.0</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="43">
         <v>8.0</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="43">
         <v>8.0</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="45" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="43">
         <v>6.0</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="43">
         <v>9.0</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="43">
         <v>12.0</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="43">
         <v>12.0</v>
       </c>
-      <c r="G15" s="43" t="s">
+      <c r="G15" s="44" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="43">
         <v>12.0</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="43">
         <v>11.0</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="43">
         <v>10.0</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="43">
         <v>9.0</v>
       </c>
-      <c r="G16" s="44" t="s">
+      <c r="G16" s="45" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="43">
         <v>20.0</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="43">
         <v>18.0</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="43">
         <v>24.0</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="43">
         <v>21.0</v>
       </c>
-      <c r="G17" s="43" t="s">
+      <c r="G17" s="44" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="43">
         <v>20.0</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="43">
         <v>19.0</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="43">
         <v>24.0</v>
       </c>
-      <c r="F18" s="42" t="s">
+      <c r="F18" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="G18" s="43" t="s">
+      <c r="G18" s="44" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="42">
+      <c r="C19" s="43">
         <v>10.0</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="43">
         <v>11.0</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="43">
         <v>12.0</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="43">
         <v>11.0</v>
       </c>
-      <c r="G19" s="43" t="s">
+      <c r="G19" s="44" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="42">
+      <c r="C20" s="43">
         <v>21.0</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="43">
         <v>22.0</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="43">
         <v>24.0</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="43">
         <v>17.0</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="44" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="43">
         <v>16.0</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="43">
         <v>15.0</v>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="43">
         <v>16.0</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="43">
         <v>14.0</v>
       </c>
-      <c r="G21" s="44" t="s">
+      <c r="G21" s="45" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="42">
+      <c r="C22" s="43">
         <v>43.0</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="43">
         <v>43.0</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="43">
         <v>60.0</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F22" s="43">
         <v>57.0</v>
       </c>
-      <c r="G22" s="43" t="s">
+      <c r="G22" s="44" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="43">
         <v>22.0</v>
       </c>
-      <c r="D23" s="42">
+      <c r="D23" s="43">
         <v>24.0</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="43">
         <v>24.0</v>
       </c>
-      <c r="F23" s="42">
+      <c r="F23" s="43">
         <v>17.0</v>
       </c>
-      <c r="G23" s="43" t="s">
+      <c r="G23" s="44" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="42">
+      <c r="C24" s="43">
         <v>12.0</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="43">
         <v>12.0</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="43">
         <v>11.0</v>
       </c>
-      <c r="F24" s="42">
+      <c r="F24" s="43">
         <v>12.0</v>
       </c>
-      <c r="G24" s="44" t="s">
+      <c r="G24" s="45" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="42">
+      <c r="C25" s="43">
         <v>60.0</v>
       </c>
-      <c r="D25" s="42">
+      <c r="D25" s="43">
         <v>54.0</v>
       </c>
-      <c r="E25" s="42">
+      <c r="E25" s="43">
         <v>72.0</v>
       </c>
-      <c r="F25" s="42">
+      <c r="F25" s="43">
         <v>63.0</v>
       </c>
-      <c r="G25" s="43" t="s">
+      <c r="G25" s="44" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="42">
+      <c r="C26" s="43">
         <v>16.0</v>
       </c>
-      <c r="D26" s="42">
+      <c r="D26" s="43">
         <v>15.0</v>
       </c>
-      <c r="E26" s="42">
+      <c r="E26" s="43">
         <v>12.0</v>
       </c>
-      <c r="F26" s="42">
+      <c r="F26" s="43">
         <v>11.0</v>
       </c>
-      <c r="G26" s="44" t="s">
+      <c r="G26" s="45" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="s">
+      <c r="A27" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="C27" s="42">
+      <c r="C27" s="43">
         <v>28.0</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="43">
         <v>26.0</v>
       </c>
-      <c r="E27" s="42">
+      <c r="E27" s="43">
         <v>30.0</v>
       </c>
-      <c r="F27" s="42">
+      <c r="F27" s="43">
         <v>14.0</v>
       </c>
-      <c r="G27" s="43" t="s">
+      <c r="G27" s="44" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="s">
+      <c r="A28" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="C28" s="42">
+      <c r="C28" s="43">
         <v>5.0</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="43">
         <v>8.0</v>
       </c>
-      <c r="E28" s="42">
+      <c r="E28" s="43">
         <v>8.0</v>
       </c>
-      <c r="F28" s="42">
+      <c r="F28" s="43">
         <v>8.0</v>
       </c>
-      <c r="G28" s="44" t="s">
+      <c r="G28" s="45" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="C29" s="42">
+      <c r="C29" s="43">
         <v>25.0</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="43">
         <v>23.0</v>
       </c>
-      <c r="E29" s="42">
+      <c r="E29" s="43">
         <v>30.0</v>
       </c>
-      <c r="F29" s="42">
+      <c r="F29" s="43">
         <v>29.0</v>
       </c>
-      <c r="G29" s="43" t="s">
+      <c r="G29" s="44" t="s">
         <v>135</v>
       </c>
     </row>
@@ -7500,68 +7532,68 @@
       <c r="G2" s="19"/>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="24">
+      <c r="C3" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="48">
         <v>1.0</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="48">
         <v>12.0</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="49">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G3" s="30"/>
+      <c r="G3" s="31"/>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="28">
+      <c r="C4" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="29">
         <v>20.0</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G4" s="19"/>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="33">
+      <c r="C5" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D5" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="34">
         <v>22.0</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="s">
@@ -7586,68 +7618,68 @@
       <c r="G6" s="19"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="24">
+      <c r="C7" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="48">
         <v>1.0</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="48">
         <v>4.0</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="49">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="28">
+      <c r="C8" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="30"/>
+      <c r="E8" s="29">
         <v>19.0</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="C9" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="34">
         <v>1.0</v>
       </c>
-      <c r="E9" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="34">
+      <c r="E9" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="s">
@@ -7672,68 +7704,68 @@
       <c r="G10" s="19"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="24">
+      <c r="C11" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="48">
         <v>1.0</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="48">
         <v>6.0</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="49">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="28">
+      <c r="C12" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="29">
         <v>22.0</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="33">
+      <c r="C13" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="34">
         <v>12.0</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="35">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="s">
@@ -7758,70 +7790,70 @@
       <c r="G14" s="19"/>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="24">
+      <c r="C15" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D15" s="48">
         <v>1.0</v>
       </c>
-      <c r="E15" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="25">
+      <c r="E15" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="49">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G15" s="19"/>
     </row>
     <row r="16">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="28">
+      <c r="C16" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="29">
         <v>1.0</v>
       </c>
-      <c r="E16" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="F16" s="29">
+      <c r="E16" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="26"/>
+      <c r="G16" s="27"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D17" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E17" s="33">
+      <c r="C17" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E17" s="34">
         <v>12.0</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="35">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="27"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="s">
@@ -7846,70 +7878,70 @@
       <c r="G18" s="19"/>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D19" s="24">
+      <c r="C19" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D19" s="48">
         <v>1.0</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="48">
         <v>6.0</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="49">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="G19" s="26"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D20" s="28">
+      <c r="C20" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D20" s="29">
         <v>1.0</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="29">
         <v>2.0</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="G20" s="26"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D21" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E21" s="33">
+      <c r="C21" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="34">
         <v>23.0</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="35">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="G21" s="26"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="s">
@@ -7934,68 +7966,68 @@
       <c r="G22" s="19"/>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D23" s="24">
+      <c r="C23" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D23" s="48">
         <v>1.0</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="48">
         <v>8.0</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="49">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G23" s="26"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="28">
+      <c r="C24" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D24" s="30"/>
+      <c r="E24" s="29">
         <v>20.0</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="G24" s="26"/>
+      <c r="G24" s="27"/>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D25" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E25" s="33">
+      <c r="C25" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D25" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E25" s="34">
         <v>21.0</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="35">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="G25" s="26"/>
+      <c r="G25" s="27"/>
     </row>
     <row r="26">
       <c r="A26" s="22" t="s">
@@ -8020,68 +8052,68 @@
       <c r="G26" s="19"/>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D27" s="24">
+      <c r="C27" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D27" s="48">
         <v>1.0</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="48">
         <v>9.0</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="49">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="G27" s="26"/>
+      <c r="G27" s="27"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="28">
+      <c r="C28" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D28" s="30"/>
+      <c r="E28" s="29">
         <v>21.0</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="30">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="G28" s="26"/>
+      <c r="G28" s="27"/>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D29" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E29" s="33">
+      <c r="C29" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D29" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E29" s="34">
         <v>23.0</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="35">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="G29" s="26"/>
+      <c r="G29" s="27"/>
     </row>
     <row r="30">
       <c r="A30" s="22" t="s">
@@ -8106,68 +8138,68 @@
       <c r="G30" s="19"/>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D31" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="E31" s="24">
+      <c r="C31" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D31" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="48">
         <v>12.0</v>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="49">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G31" s="26"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="F32" s="29">
+      <c r="C32" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D32" s="30"/>
+      <c r="E32" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="F32" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="34">
+      <c r="C33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G33" s="26"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34">
       <c r="A34" s="22" t="s">
@@ -8192,68 +8224,68 @@
       <c r="G34" s="19"/>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="25">
+      <c r="C35" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="49">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G35" s="26"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D36" s="29"/>
-      <c r="E36" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="F36" s="29">
+      <c r="C36" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D36" s="30"/>
+      <c r="E36" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="F36" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="27"/>
     </row>
     <row r="37">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="32" t="s">
+      <c r="B37" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D37" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E37" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="F37" s="34">
+      <c r="C37" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D37" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E37" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="F37" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G37" s="26"/>
+      <c r="G37" s="27"/>
     </row>
     <row r="38">
       <c r="A38" s="22" t="s">
@@ -8278,68 +8310,68 @@
       <c r="G38" s="19"/>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D39" s="24">
+      <c r="C39" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D39" s="48">
         <v>1.0</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="48">
         <v>18.0</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="49">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="G39" s="26"/>
+      <c r="G39" s="27"/>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D40" s="29"/>
-      <c r="E40" s="28">
+      <c r="C40" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D40" s="30"/>
+      <c r="E40" s="29">
         <v>19.0</v>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="30">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="G40" s="26"/>
+      <c r="G40" s="27"/>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D41" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E41" s="33">
+      <c r="C41" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D41" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E41" s="34">
         <v>19.0</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="35">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="G41" s="26"/>
+      <c r="G41" s="27"/>
     </row>
     <row r="42">
       <c r="A42" s="22" t="s">
@@ -8364,70 +8396,70 @@
       <c r="G42" s="19"/>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D43" s="24">
+      <c r="C43" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D43" s="48">
         <v>2.0</v>
       </c>
-      <c r="E43" s="24">
+      <c r="E43" s="48">
         <v>17.0</v>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="49">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="G43" s="26"/>
+      <c r="G43" s="27"/>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D44" s="28">
+      <c r="C44" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D44" s="29">
         <v>1.0</v>
       </c>
-      <c r="E44" s="28">
+      <c r="E44" s="29">
         <v>15.0</v>
       </c>
-      <c r="F44" s="29">
+      <c r="F44" s="30">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G44" s="26"/>
+      <c r="G44" s="27"/>
     </row>
     <row r="45">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D45" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E45" s="33">
+      <c r="C45" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D45" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E45" s="34">
         <v>16.0</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="35">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="G45" s="26"/>
+      <c r="G45" s="27"/>
     </row>
     <row r="46">
       <c r="A46" s="22" t="s">
@@ -8452,70 +8484,70 @@
       <c r="G46" s="19"/>
     </row>
     <row r="47">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D47" s="24">
+      <c r="C47" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D47" s="48">
         <v>3.0</v>
       </c>
-      <c r="E47" s="24">
+      <c r="E47" s="48">
         <v>5.0</v>
       </c>
-      <c r="F47" s="25">
+      <c r="F47" s="49">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G47" s="26"/>
+      <c r="G47" s="27"/>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D48" s="28">
+      <c r="C48" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D48" s="29">
         <v>1.0</v>
       </c>
-      <c r="E48" s="28">
+      <c r="E48" s="29">
         <v>3.0</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="30">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G48" s="26"/>
+      <c r="G48" s="27"/>
     </row>
     <row r="49">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D49" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E49" s="33">
+      <c r="C49" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D49" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E49" s="34">
         <v>19.0</v>
       </c>
-      <c r="F49" s="34">
+      <c r="F49" s="35">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="G49" s="26"/>
+      <c r="G49" s="27"/>
     </row>
     <row r="50">
       <c r="A50" s="22" t="s">
@@ -8540,70 +8572,70 @@
       <c r="G50" s="19"/>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D51" s="24">
+      <c r="C51" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D51" s="48">
         <v>3.0</v>
       </c>
-      <c r="E51" s="24">
+      <c r="E51" s="48">
         <v>1.0</v>
       </c>
-      <c r="F51" s="25">
+      <c r="F51" s="49">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G51" s="26"/>
+      <c r="G51" s="27"/>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D52" s="28">
+      <c r="C52" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D52" s="29">
         <v>1.0</v>
       </c>
-      <c r="E52" s="28">
+      <c r="E52" s="29">
         <v>14.0</v>
       </c>
-      <c r="F52" s="29">
+      <c r="F52" s="30">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="G52" s="26"/>
+      <c r="G52" s="27"/>
     </row>
     <row r="53">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C53" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D53" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E53" s="33">
+      <c r="C53" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D53" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E53" s="34">
         <v>21.0</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="35">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="G53" s="26"/>
+      <c r="G53" s="27"/>
     </row>
     <row r="54">
       <c r="A54" s="22" t="s">
@@ -8628,68 +8660,68 @@
       <c r="G54" s="19"/>
     </row>
     <row r="55">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C55" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D55" s="24">
+      <c r="C55" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D55" s="48">
         <v>1.0</v>
       </c>
-      <c r="E55" s="24">
+      <c r="E55" s="48">
         <v>14.0</v>
       </c>
-      <c r="F55" s="25">
+      <c r="F55" s="49">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="G55" s="26"/>
+      <c r="G55" s="27"/>
     </row>
     <row r="56">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C56" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D56" s="29"/>
-      <c r="E56" s="28">
+      <c r="C56" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D56" s="30"/>
+      <c r="E56" s="29">
         <v>17.0</v>
       </c>
-      <c r="F56" s="29">
+      <c r="F56" s="30">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="G56" s="26"/>
+      <c r="G56" s="27"/>
     </row>
     <row r="57">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="32" t="s">
+      <c r="B57" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C57" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D57" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E57" s="33">
+      <c r="C57" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D57" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E57" s="34">
         <v>16.0</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="G57" s="26"/>
+      <c r="G57" s="27"/>
     </row>
     <row r="58">
       <c r="A58" s="22" t="s">
@@ -8714,70 +8746,70 @@
       <c r="G58" s="19"/>
     </row>
     <row r="59">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B59" s="23" t="s">
+      <c r="B59" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C59" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D59" s="24">
+      <c r="C59" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D59" s="48">
         <v>1.0</v>
       </c>
-      <c r="E59" s="24">
+      <c r="E59" s="48">
         <v>22.0</v>
       </c>
-      <c r="F59" s="25">
+      <c r="F59" s="49">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="G59" s="26"/>
+      <c r="G59" s="27"/>
     </row>
     <row r="60">
-      <c r="A60" s="27" t="s">
+      <c r="A60" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C60" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D60" s="28">
+      <c r="C60" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D60" s="29">
         <v>1.0</v>
       </c>
-      <c r="E60" s="28">
+      <c r="E60" s="29">
         <v>12.0</v>
       </c>
-      <c r="F60" s="29">
+      <c r="F60" s="30">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G60" s="26"/>
+      <c r="G60" s="27"/>
     </row>
     <row r="61">
-      <c r="A61" s="31" t="s">
+      <c r="A61" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="C61" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D61" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E61" s="33">
+      <c r="C61" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D61" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E61" s="34">
         <v>14.0</v>
       </c>
-      <c r="F61" s="34">
+      <c r="F61" s="35">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="G61" s="26"/>
+      <c r="G61" s="27"/>
     </row>
     <row r="62">
       <c r="A62" s="22" t="s">
@@ -8802,70 +8834,70 @@
       <c r="G62" s="19"/>
     </row>
     <row r="63">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="B63" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="D63" s="24">
+      <c r="C63" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D63" s="48">
         <v>2.0</v>
       </c>
-      <c r="E63" s="24">
+      <c r="E63" s="48">
         <v>9.0</v>
       </c>
-      <c r="F63" s="25">
+      <c r="F63" s="49">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="G63" s="30"/>
+      <c r="G63" s="31"/>
     </row>
     <row r="64">
-      <c r="A64" s="27" t="s">
+      <c r="A64" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C64" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="D64" s="28">
+      <c r="C64" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="D64" s="29">
         <v>1.0</v>
       </c>
-      <c r="E64" s="28">
+      <c r="E64" s="29">
         <v>1.0</v>
       </c>
-      <c r="F64" s="29">
+      <c r="F64" s="30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G64" s="30"/>
+      <c r="G64" s="31"/>
     </row>
     <row r="65">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B65" s="32" t="s">
+      <c r="B65" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C65" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D65" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E65" s="33">
+      <c r="C65" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D65" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E65" s="34">
         <v>19.0</v>
       </c>
-      <c r="F65" s="34">
+      <c r="F65" s="35">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="G65" s="30"/>
+      <c r="G65" s="31"/>
     </row>
     <row r="66">
       <c r="A66" s="22" t="s">
@@ -8874,13 +8906,13 @@
       <c r="B66" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C66" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="D66" s="47">
+      <c r="C66" s="51">
+        <v>0.0</v>
+      </c>
+      <c r="D66" s="51">
         <v>3.0</v>
       </c>
-      <c r="E66" s="47">
+      <c r="E66" s="51">
         <v>16.0</v>
       </c>
       <c r="F66" s="18">
@@ -8889,70 +8921,70 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="23" t="s">
+      <c r="A67" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="23" t="s">
+      <c r="B67" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="C67" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="D67" s="48">
+      <c r="C67" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="D67" s="52">
         <v>7.0</v>
       </c>
-      <c r="E67" s="48">
+      <c r="E67" s="52">
         <v>13.0</v>
       </c>
-      <c r="F67" s="25">
+      <c r="F67" s="49">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="G67" s="30"/>
+      <c r="G67" s="31"/>
     </row>
     <row r="68">
-      <c r="A68" s="27" t="s">
+      <c r="A68" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C68" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D68" s="49">
+      <c r="C68" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="D68" s="53">
         <v>3.0</v>
       </c>
-      <c r="E68" s="49">
+      <c r="E68" s="53">
         <v>7.0</v>
       </c>
-      <c r="F68" s="29">
+      <c r="F68" s="30">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G68" s="30"/>
+      <c r="G68" s="31"/>
     </row>
     <row r="69">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B69" s="32" t="s">
+      <c r="B69" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D69" s="35">
+      <c r="C69" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D69" s="36">
         <v>1.0</v>
       </c>
-      <c r="E69" s="35">
+      <c r="E69" s="36">
         <v>1.0</v>
       </c>
-      <c r="F69" s="34">
+      <c r="F69" s="35">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G69" s="30"/>
+      <c r="G69" s="31"/>
     </row>
     <row r="70">
       <c r="A70" s="22" t="s">
@@ -8961,13 +8993,13 @@
       <c r="B70" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C70" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="D70" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="E70" s="47">
+      <c r="C70" s="51">
+        <v>0.0</v>
+      </c>
+      <c r="D70" s="51">
+        <v>0.0</v>
+      </c>
+      <c r="E70" s="51">
         <v>0.0</v>
       </c>
       <c r="F70" s="18">
@@ -8976,70 +9008,70 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="23" t="s">
+      <c r="A71" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="23" t="s">
+      <c r="B71" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="C71" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="D71" s="48">
+      <c r="C71" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="D71" s="52">
         <v>2.0</v>
       </c>
-      <c r="E71" s="48">
+      <c r="E71" s="52">
         <v>18.0</v>
       </c>
-      <c r="F71" s="25">
+      <c r="F71" s="49">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="G71" s="30"/>
+      <c r="G71" s="31"/>
     </row>
     <row r="72">
-      <c r="A72" s="27" t="s">
+      <c r="A72" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C72" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D72" s="49">
+      <c r="C72" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="D72" s="53">
         <v>1.0</v>
       </c>
-      <c r="E72" s="49">
+      <c r="E72" s="53">
         <v>15.0</v>
       </c>
-      <c r="F72" s="29">
+      <c r="F72" s="30">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G72" s="30"/>
+      <c r="G72" s="31"/>
     </row>
     <row r="73">
-      <c r="A73" s="31" t="s">
+      <c r="A73" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="32" t="s">
+      <c r="B73" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C73" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D73" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E73" s="35">
+      <c r="C73" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D73" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E73" s="36">
         <v>23.0</v>
       </c>
-      <c r="F73" s="34">
+      <c r="F73" s="35">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="G73" s="30"/>
+      <c r="G73" s="31"/>
     </row>
     <row r="74">
       <c r="A74" s="22" t="s">
@@ -9048,13 +9080,13 @@
       <c r="B74" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="D74" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="E74" s="47">
+      <c r="C74" s="51">
+        <v>0.0</v>
+      </c>
+      <c r="D74" s="51">
+        <v>0.0</v>
+      </c>
+      <c r="E74" s="51">
         <v>0.0</v>
       </c>
       <c r="F74" s="18">
@@ -9063,70 +9095,70 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B75" s="23" t="s">
+      <c r="B75" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="C75" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="D75" s="48">
+      <c r="C75" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="D75" s="52">
         <v>3.0</v>
       </c>
-      <c r="E75" s="48">
+      <c r="E75" s="52">
         <v>9.0</v>
       </c>
-      <c r="F75" s="25">
+      <c r="F75" s="49">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="G75" s="30"/>
+      <c r="G75" s="31"/>
     </row>
     <row r="76">
-      <c r="A76" s="27" t="s">
+      <c r="A76" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C76" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D76" s="49">
+      <c r="C76" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="D76" s="53">
         <v>1.0</v>
       </c>
-      <c r="E76" s="49">
+      <c r="E76" s="53">
         <v>8.0</v>
       </c>
-      <c r="F76" s="29">
+      <c r="F76" s="30">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G76" s="30"/>
+      <c r="G76" s="31"/>
     </row>
     <row r="77">
-      <c r="A77" s="31" t="s">
+      <c r="A77" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="32" t="s">
+      <c r="B77" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C77" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D77" s="35">
+      <c r="C77" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D77" s="36">
         <v>1.0</v>
       </c>
-      <c r="E77" s="35">
+      <c r="E77" s="36">
         <v>12.0</v>
       </c>
-      <c r="F77" s="34">
+      <c r="F77" s="35">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G77" s="30"/>
+      <c r="G77" s="31"/>
     </row>
     <row r="78">
       <c r="A78" s="22" t="s">
@@ -9135,13 +9167,13 @@
       <c r="B78" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C78" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="D78" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="E78" s="47">
+      <c r="C78" s="51">
+        <v>0.0</v>
+      </c>
+      <c r="D78" s="51">
+        <v>0.0</v>
+      </c>
+      <c r="E78" s="51">
         <v>0.0</v>
       </c>
       <c r="F78" s="18">
@@ -9150,69 +9182,69 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="23" t="s">
+      <c r="A79" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B79" s="23" t="s">
+      <c r="B79" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C79" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="D79" s="48">
+      <c r="C79" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="D79" s="52">
         <v>16.0</v>
       </c>
-      <c r="E79" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="F79" s="25">
+      <c r="E79" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="F79" s="49">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="27" t="s">
+      <c r="A80" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="C80" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D80" s="49">
+      <c r="C80" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="D80" s="53">
         <v>1.0</v>
       </c>
-      <c r="E80" s="49">
+      <c r="E80" s="53">
         <v>5.0</v>
       </c>
-      <c r="F80" s="29">
+      <c r="F80" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G80" s="30"/>
+      <c r="G80" s="31"/>
     </row>
     <row r="81">
-      <c r="A81" s="31" t="s">
+      <c r="A81" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B81" s="32" t="s">
+      <c r="B81" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="C81" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D81" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E81" s="35">
+      <c r="C81" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D81" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E81" s="36">
         <v>4.0</v>
       </c>
-      <c r="F81" s="34">
+      <c r="F81" s="35">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="G81" s="30"/>
+      <c r="G81" s="31"/>
     </row>
     <row r="82">
       <c r="A82" s="22" t="s">
@@ -9221,13 +9253,13 @@
       <c r="B82" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C82" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="D82" s="47">
+      <c r="C82" s="51">
+        <v>0.0</v>
+      </c>
+      <c r="D82" s="51">
         <v>2.0</v>
       </c>
-      <c r="E82" s="47">
+      <c r="E82" s="51">
         <v>0.0</v>
       </c>
       <c r="F82" s="18">
@@ -9236,69 +9268,69 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="23" t="s">
+      <c r="A83" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B83" s="23" t="s">
+      <c r="B83" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="C83" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="D83" s="48">
+      <c r="C83" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="D83" s="52">
         <v>10.0</v>
       </c>
-      <c r="E83" s="48">
+      <c r="E83" s="52">
         <v>9.0</v>
       </c>
-      <c r="F83" s="25">
+      <c r="F83" s="49">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="27" t="s">
+      <c r="A84" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B84" s="27" t="s">
+      <c r="B84" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C84" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D84" s="49">
+      <c r="C84" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="D84" s="53">
         <v>1.0</v>
       </c>
-      <c r="E84" s="49">
+      <c r="E84" s="53">
         <v>3.0</v>
       </c>
-      <c r="F84" s="29">
+      <c r="F84" s="30">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G84" s="30"/>
+      <c r="G84" s="31"/>
     </row>
     <row r="85">
-      <c r="A85" s="31" t="s">
+      <c r="A85" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B85" s="32" t="s">
+      <c r="B85" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="C85" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="D85" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="E85" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="F85" s="34">
+      <c r="C85" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="D85" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E85" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="F85" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G85" s="30"/>
+      <c r="G85" s="31"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$Z$85">
